--- a/Lab 4/Scenario 1.xlsx
+++ b/Lab 4/Scenario 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fs09911\Desktop\Database-Systems-Labs\Lab 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED0D759-53A3-4141-8168-7EF57E290AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE86A765-660B-45F9-ADDA-4A0D2856FEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="49">
   <si>
     <t>1NF</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Guardian</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -662,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N6"/>
+  <dimension ref="B1:N10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -812,6 +815,11 @@
       </c>
       <c r="N6" s="12" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:H30"/>
+  <dimension ref="B1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -924,6 +932,12 @@
         <v>6</v>
       </c>
       <c r="C9" s="1"/>
+      <c r="E9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
@@ -932,6 +946,18 @@
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="E10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
@@ -940,6 +966,18 @@
       <c r="C11" s="12" t="s">
         <v>20</v>
       </c>
+      <c r="E11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
@@ -948,142 +986,96 @@
       <c r="C12" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="E12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="F15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="H16" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="G17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="H17" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="H18" s="12" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
@@ -1094,19 +1086,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:F36"/>
+  <dimension ref="B1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="15" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>31</v>
       </c>
@@ -1114,8 +1106,12 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
@@ -1131,8 +1127,14 @@
       <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
@@ -1148,8 +1150,14 @@
       <c r="F5" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
@@ -1165,15 +1173,27 @@
       <c r="F6" s="12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1183,8 +1203,20 @@
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>25</v>
       </c>
@@ -1194,8 +1226,20 @@
       <c r="D11" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
         <v>36</v>
       </c>
@@ -1205,175 +1249,99 @@
       <c r="D12" s="12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="G15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="H18" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="I18" s="12" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F9:I9"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
